--- a/data/merged/2026-09-28/MERGED_DE_Mite-Vacuum_2026-09-28.xlsx
+++ b/data/merged/2026-09-28/MERGED_DE_Mite-Vacuum_2026-09-28.xlsx
@@ -5648,50 +5648,6 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>47</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>47</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="28" name="Product 28">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <ns2:creationId id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId28" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -6017,7 +5973,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BR51"/>
+  <dimension ref="A1:BR50"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" style="1" customWidth="1"/>
@@ -17320,52 +17276,40 @@
       <c r="B48" s="13"/>
       <c r="C48" s="14" t="inlineStr">
         <is>
-          <t>B0GH912PFJ</t>
+          <t>B0D7HF8S2W</t>
         </is>
       </c>
       <c r="D48" s="14"/>
-      <c r="E48" s="14" t="inlineStr">
-        <is>
-          <t>Marke: KÄRCHER | Kompatible Geräte: Kärcher VCH 4 UVClean | Produktabmessungen: 6,4L x 3,2B x 5H cm | Wiederverwendbarkeit: Wiederverwendbar | Stückzahl: 6</t>
-        </is>
-      </c>
+      <c r="E48" s="14"/>
       <c r="F48" s="14" t="inlineStr">
         <is>
-          <t>KÄRCHER</t>
+          <t>Minthouz</t>
         </is>
       </c>
       <c r="G48" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.de/stores/K%C3%A4rcher/page/EFE3653A-1163-432C-A85B-0486A31C0E3D?lp_asin=B0GH912PFJ&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.de/stores/Minthouz/page/08953CA0-3566-47FB-BCE8-A230ADB3247F?lp_asin=B0D7HF8S2W&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
         </is>
       </c>
       <c r="H48" s="14" t="inlineStr">
         <is>
-          <t>KÄRCHER Filter-Set für VCH 4 UVClean Matratzenreiniger, Ersatzfilter aus Motorschutzfilter und Schaumfilter für hygienische Reinigung, 1 Set</t>
-        </is>
-      </c>
-      <c r="I48" s="14" t="inlineStr">
-        <is>
-          <t>Filterset für eine konstant hohe hygienische Reinigungsleistung bei der Matratzenreinigung
-Hält Feinstaub, Milben, Bakterien und Hautschuppen zuverlässig und effektiv zurück
-Die doppelte Filterbarriere schützt den Motor zuverlässig vor Verschleiß und erhöht die Langlebigkeit
-Einfacher und schneller Austausch
-Kompatibel mit dem Kärcher Matratzenreiniger VCH 4 UVClean</t>
-        </is>
-      </c>
+          <t>Minthouz Milbensauger für Matratzen, 15 Kpa Milbensauger mit UV Licht, Intelligente Staubsensierung, 60 ℃ Heiße Luft, 450 W M</t>
+        </is>
+      </c>
+      <c r="I48" s="14"/>
       <c r="J48" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.de/dp/B0GH912PFJ?psc=1</t>
+          <t>https://www.amazon.de/dp/B0D7HF8S2W?psc=1</t>
         </is>
       </c>
       <c r="K48" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T3/images/I/51GeVSsTnnL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/61pssUlO3ZL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L48" s="14" t="inlineStr">
         <is>
-          <t>B0GH912PFJ</t>
+          <t>B0D7HF8S2W</t>
         </is>
       </c>
       <c r="M48" s="14" t="inlineStr">
@@ -17379,13 +17323,13 @@
         </is>
       </c>
       <c r="O48" s="15">
-        <v>85516</v>
+        <v>1186089</v>
       </c>
       <c r="P48" s="15">
-        <v>737201</v>
+        <v>-6525</v>
       </c>
       <c r="Q48" s="16">
-        <v>0.88</v>
+        <v>-0.01</v>
       </c>
       <c r="R48" s="17" t="inlineStr">
         <is>
@@ -17394,140 +17338,152 @@
       </c>
       <c r="S48" s="18" t="inlineStr">
         <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="T48" s="15">
-        <v>6</v>
-      </c>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="T48" s="15"/>
       <c r="U48" s="16"/>
-      <c r="V48" s="15">
-        <v>60</v>
-      </c>
+      <c r="V48" s="15"/>
       <c r="W48" s="15"/>
       <c r="X48" s="15"/>
       <c r="Y48" s="19">
         <v>1</v>
       </c>
       <c r="Z48" s="20">
-        <v>9.55</v>
+        <v>59.99</v>
       </c>
       <c r="AA48" s="4"/>
       <c r="AB48" s="1"/>
       <c r="AC48" s="15"/>
       <c r="AD48" s="19">
-        <v>1</v>
+        <v>88</v>
       </c>
       <c r="AE48" s="15">
         <v>0</v>
       </c>
       <c r="AF48" s="21">
-        <v>5</v>
+        <v>3.1</v>
       </c>
       <c r="AG48" s="22">
         <v>0</v>
       </c>
       <c r="AH48" s="20">
-        <v>3.08</v>
+        <v>5.29</v>
       </c>
       <c r="AI48" s="16">
-        <v>0.54</v>
+        <v>0.76</v>
       </c>
       <c r="AJ48"/>
       <c r="AK48" s="13" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="AL48" s="19">
-        <v>231</v>
+        <v>753</v>
       </c>
       <c r="AM48" s="13" t="inlineStr">
         <is>
-          <t>AMZ</t>
+          <t>FBA</t>
         </is>
       </c>
       <c r="AN48" s="13"/>
       <c r="AO48" s="13"/>
-      <c r="AP48" s="20">
-        <v>11.17</v>
-      </c>
-      <c r="AQ48" s="19"/>
+      <c r="AP48" s="20"/>
+      <c r="AQ48" s="19">
+        <v>9</v>
+      </c>
       <c r="AR48" s="19">
         <v>1</v>
       </c>
       <c r="AS48" s="14" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Minthouz EUDirect</t>
         </is>
       </c>
       <c r="AT48" s="13" t="inlineStr">
         <is>
-          <t>AMZ</t>
-        </is>
-      </c>
-      <c r="AU48" s="13"/>
-      <c r="AV48" s="14"/>
-      <c r="AW48" s="13"/>
+          <t>FBA</t>
+        </is>
+      </c>
+      <c r="AU48" s="13" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="AV48" s="14" t="inlineStr">
+        <is>
+          <t>guangmingqu Guangdong 518100 CN</t>
+        </is>
+      </c>
+      <c r="AW48" s="13" t="inlineStr">
+        <is>
+          <t>https://www.amazon.de/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A33KFCZH4G272M</t>
+        </is>
+      </c>
       <c r="AX48" s="13"/>
       <c r="AY48" s="13"/>
       <c r="AZ48" s="13"/>
       <c r="BA48" s="13"/>
       <c r="BB48" s="13"/>
-      <c r="BC48" s="13"/>
-      <c r="BD48" s="13"/>
+      <c r="BC48" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="BD48" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BE48" s="13"/>
-      <c r="BF48" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BF48" s="13"/>
       <c r="BG48" s="13"/>
       <c r="BH48" s="14"/>
       <c r="BI48" s="23"/>
       <c r="BJ48" s="23" t="inlineStr">
         <is>
-          <t>10 g</t>
+          <t>3.6 kg</t>
         </is>
       </c>
       <c r="BK48" s="23" t="inlineStr">
         <is>
-          <t>10.00 g</t>
+          <t>3.60 kg</t>
         </is>
       </c>
       <c r="BL48" s="23" t="inlineStr">
         <is>
-          <t>6.4 x 3.2 x 5 cm</t>
+          <t>26.2 x 17.5 x 25.5 cm</t>
         </is>
       </c>
       <c r="BM48" s="23" t="inlineStr">
         <is>
-          <t>6.40 x 3.20 x 5.00 cm</t>
+          <t>26.20 x 17.50 x 25.50 cm</t>
         </is>
       </c>
       <c r="BN48" s="23" t="inlineStr">
         <is>
-          <t>20 g</t>
+          <t>3.89 kg</t>
         </is>
       </c>
       <c r="BO48" s="23" t="inlineStr">
         <is>
-          <t>20.00 g</t>
+          <t>3.89 kg</t>
         </is>
       </c>
       <c r="BP48" s="23" t="inlineStr">
         <is>
-          <t>9.6 x 6.6 x 4.7 cm</t>
+          <t>32.7 x 32.3 x 25.4 cm</t>
         </is>
       </c>
       <c r="BQ48" s="23" t="inlineStr">
         <is>
-          <t>9.60 x 6.60 x 4.70 cm</t>
+          <t>32.70 x 32.30 x 25.40 cm</t>
         </is>
       </c>
       <c r="BR48" s="13" t="inlineStr">
         <is>
-          <t>超大号信封</t>
+          <t>标准包裹</t>
         </is>
       </c>
     </row>
@@ -17538,216 +17494,106 @@
       <c r="B49" s="13"/>
       <c r="C49" s="14" t="inlineStr">
         <is>
-          <t>B0D7HF8S2W</t>
+          <t>B0F8J7PQHF</t>
         </is>
       </c>
       <c r="D49" s="14"/>
       <c r="E49" s="14"/>
-      <c r="F49" s="14" t="inlineStr">
-        <is>
-          <t>Minthouz</t>
-        </is>
-      </c>
+      <c r="F49" s="14"/>
       <c r="G49" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.de/stores/Minthouz/page/08953CA0-3566-47FB-BCE8-A230ADB3247F?lp_asin=B0D7HF8S2W&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+          <t>https://www.amazon.deundefined</t>
         </is>
       </c>
       <c r="H49" s="14" t="inlineStr">
         <is>
-          <t>Minthouz Milbensauger für Matratzen, 15 Kpa Milbensauger mit UV Licht, Intelligente Staubsensierung, 60 ℃ Heiße Luft, 450 W M</t>
+          <t>Cecotec Handstaubsauger für Matratzen und Polster Conga Rockstar 3000 Mattress Essential. 300W, 10 kPa, Ultraviolettes Licht</t>
         </is>
       </c>
       <c r="I49" s="14"/>
       <c r="J49" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.de/dp/B0D7HF8S2W?psc=1</t>
+          <t>https://www.amazon.de/dp/B0F8J7PQHF?psc=1</t>
         </is>
       </c>
       <c r="K49" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/61pssUlO3ZL._AC_US600_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71X71xtiqiL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L49" s="14" t="inlineStr">
         <is>
-          <t>B0D7HF8S2W</t>
-        </is>
-      </c>
-      <c r="M49" s="14" t="inlineStr">
-        <is>
-          <t>Küche, Haushalt &amp; Wohnen:Haushaltsreiniger &amp; Staubsauger:Staubsauger:Matratzensauger</t>
-        </is>
-      </c>
-      <c r="N49" s="14" t="inlineStr">
-        <is>
-          <t>Küche, Haushalt &amp; Wohnen</t>
-        </is>
-      </c>
-      <c r="O49" s="15">
-        <v>1186089</v>
-      </c>
-      <c r="P49" s="15">
-        <v>-6525</v>
-      </c>
-      <c r="Q49" s="16">
-        <v>-0.01</v>
-      </c>
-      <c r="R49" s="17" t="inlineStr">
-        <is>
-          <t>Matratzensauger</t>
-        </is>
-      </c>
-      <c r="S49" s="18" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
+          <t>B0F8J7PQHF</t>
+        </is>
+      </c>
+      <c r="M49" s="14"/>
+      <c r="N49" s="14"/>
+      <c r="O49" s="15"/>
+      <c r="P49" s="15"/>
+      <c r="Q49" s="16"/>
+      <c r="R49" s="17"/>
+      <c r="S49" s="18"/>
       <c r="T49" s="15"/>
       <c r="U49" s="16"/>
       <c r="V49" s="15"/>
       <c r="W49" s="15"/>
       <c r="X49" s="15"/>
-      <c r="Y49" s="19">
-        <v>1</v>
-      </c>
+      <c r="Y49" s="19"/>
       <c r="Z49" s="20">
-        <v>59.99</v>
+        <v>42.96</v>
       </c>
       <c r="AA49" s="4"/>
       <c r="AB49" s="1"/>
       <c r="AC49" s="15"/>
       <c r="AD49" s="19">
-        <v>88</v>
-      </c>
-      <c r="AE49" s="15">
-        <v>0</v>
-      </c>
+        <v>849</v>
+      </c>
+      <c r="AE49" s="15"/>
       <c r="AF49" s="21">
-        <v>3.1</v>
+        <v>4.3</v>
       </c>
       <c r="AG49" s="22">
         <v>0</v>
       </c>
-      <c r="AH49" s="20">
-        <v>5.29</v>
-      </c>
+      <c r="AH49" s="20"/>
       <c r="AI49" s="16">
-        <v>0.76</v>
+        <v>0</v>
       </c>
       <c r="AJ49"/>
-      <c r="AK49" s="13" t="inlineStr">
-        <is>
-          <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="AL49" s="19">
-        <v>753</v>
-      </c>
-      <c r="AM49" s="13" t="inlineStr">
-        <is>
-          <t>FBA</t>
-        </is>
-      </c>
+      <c r="AK49" s="13"/>
+      <c r="AL49" s="19"/>
+      <c r="AM49" s="13"/>
       <c r="AN49" s="13"/>
       <c r="AO49" s="13"/>
       <c r="AP49" s="20"/>
-      <c r="AQ49" s="19">
-        <v>9</v>
-      </c>
-      <c r="AR49" s="19">
-        <v>1</v>
-      </c>
-      <c r="AS49" s="14" t="inlineStr">
-        <is>
-          <t>Minthouz EUDirect</t>
-        </is>
-      </c>
-      <c r="AT49" s="13" t="inlineStr">
-        <is>
-          <t>FBA</t>
-        </is>
-      </c>
-      <c r="AU49" s="13" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="AV49" s="14" t="inlineStr">
-        <is>
-          <t>guangmingqu Guangdong 518100 CN</t>
-        </is>
-      </c>
-      <c r="AW49" s="13" t="inlineStr">
-        <is>
-          <t>https://www.amazon.de/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A33KFCZH4G272M</t>
-        </is>
-      </c>
+      <c r="AQ49" s="19"/>
+      <c r="AR49" s="19"/>
+      <c r="AS49" s="14"/>
+      <c r="AT49" s="13"/>
+      <c r="AU49" s="13"/>
+      <c r="AV49" s="14"/>
+      <c r="AW49" s="13"/>
       <c r="AX49" s="13"/>
       <c r="AY49" s="13"/>
       <c r="AZ49" s="13"/>
       <c r="BA49" s="13"/>
       <c r="BB49" s="13"/>
-      <c r="BC49" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BD49" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BC49" s="13"/>
+      <c r="BD49" s="13"/>
       <c r="BE49" s="13"/>
       <c r="BF49" s="13"/>
       <c r="BG49" s="13"/>
       <c r="BH49" s="14"/>
       <c r="BI49" s="23"/>
-      <c r="BJ49" s="23" t="inlineStr">
-        <is>
-          <t>3.6 kg</t>
-        </is>
-      </c>
-      <c r="BK49" s="23" t="inlineStr">
-        <is>
-          <t>3.60 kg</t>
-        </is>
-      </c>
-      <c r="BL49" s="23" t="inlineStr">
-        <is>
-          <t>26.2 x 17.5 x 25.5 cm</t>
-        </is>
-      </c>
-      <c r="BM49" s="23" t="inlineStr">
-        <is>
-          <t>26.20 x 17.50 x 25.50 cm</t>
-        </is>
-      </c>
-      <c r="BN49" s="23" t="inlineStr">
-        <is>
-          <t>3.89 kg</t>
-        </is>
-      </c>
-      <c r="BO49" s="23" t="inlineStr">
-        <is>
-          <t>3.89 kg</t>
-        </is>
-      </c>
-      <c r="BP49" s="23" t="inlineStr">
-        <is>
-          <t>32.7 x 32.3 x 25.4 cm</t>
-        </is>
-      </c>
-      <c r="BQ49" s="23" t="inlineStr">
-        <is>
-          <t>32.70 x 32.30 x 25.40 cm</t>
-        </is>
-      </c>
-      <c r="BR49" s="13" t="inlineStr">
-        <is>
-          <t>标准包裹</t>
-        </is>
-      </c>
+      <c r="BJ49" s="23"/>
+      <c r="BK49" s="23"/>
+      <c r="BL49" s="23"/>
+      <c r="BM49" s="23"/>
+      <c r="BN49" s="23"/>
+      <c r="BO49" s="23"/>
+      <c r="BP49" s="23"/>
+      <c r="BQ49" s="23"/>
+      <c r="BR49" s="13"/>
     </row>
     <row r="50" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="13">
@@ -17756,7 +17602,7 @@
       <c r="B50" s="13"/>
       <c r="C50" s="14" t="inlineStr">
         <is>
-          <t>B0F8J7PQHF</t>
+          <t>B0F93T73PK</t>
         </is>
       </c>
       <c r="D50" s="14"/>
@@ -17769,23 +17615,23 @@
       </c>
       <c r="H50" s="14" t="inlineStr">
         <is>
-          <t>Cecotec Handstaubsauger für Matratzen und Polster Conga Rockstar 3000 Mattress Essential. 300W, 10 kPa, Ultraviolettes Licht</t>
+          <t>Brandson - Milbensauger für Matratzen mit UV Licht - Handstaubsauger − UV-C Sterilisationslicht − Hepa Filter – Bürstenwalze</t>
         </is>
       </c>
       <c r="I50" s="14"/>
       <c r="J50" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.de/dp/B0F8J7PQHF?psc=1</t>
+          <t>https://www.amazon.de/dp/B0F93T73PK?psc=1</t>
         </is>
       </c>
       <c r="K50" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71X71xtiqiL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/719oPgCjpQL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L50" s="14" t="inlineStr">
         <is>
-          <t>B0F8J7PQHF</t>
+          <t>B0F93T73PK</t>
         </is>
       </c>
       <c r="M50" s="14"/>
@@ -17801,18 +17647,16 @@
       <c r="W50" s="15"/>
       <c r="X50" s="15"/>
       <c r="Y50" s="19"/>
-      <c r="Z50" s="20">
-        <v>42.96</v>
-      </c>
+      <c r="Z50" s="20"/>
       <c r="AA50" s="4"/>
       <c r="AB50" s="1"/>
       <c r="AC50" s="15"/>
       <c r="AD50" s="19">
-        <v>849</v>
+        <v>26</v>
       </c>
       <c r="AE50" s="15"/>
       <c r="AF50" s="21">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="AG50" s="22">
         <v>0</v>
@@ -17856,112 +17700,6 @@
       <c r="BP50" s="23"/>
       <c r="BQ50" s="23"/>
       <c r="BR50" s="13"/>
-    </row>
-    <row r="51" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="13">
-        <v>50</v>
-      </c>
-      <c r="B51" s="13"/>
-      <c r="C51" s="14" t="inlineStr">
-        <is>
-          <t>B0F93T73PK</t>
-        </is>
-      </c>
-      <c r="D51" s="14"/>
-      <c r="E51" s="14"/>
-      <c r="F51" s="14"/>
-      <c r="G51" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.deundefined</t>
-        </is>
-      </c>
-      <c r="H51" s="14" t="inlineStr">
-        <is>
-          <t>Brandson - Milbensauger für Matratzen mit UV Licht - Handstaubsauger − UV-C Sterilisationslicht − Hepa Filter – Bürstenwalze</t>
-        </is>
-      </c>
-      <c r="I51" s="14"/>
-      <c r="J51" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.de/dp/B0F93T73PK?psc=1</t>
-        </is>
-      </c>
-      <c r="K51" s="14" t="inlineStr">
-        <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/719oPgCjpQL._AC_UL300_SR300,200_.jpg</t>
-        </is>
-      </c>
-      <c r="L51" s="14" t="inlineStr">
-        <is>
-          <t>B0F93T73PK</t>
-        </is>
-      </c>
-      <c r="M51" s="14"/>
-      <c r="N51" s="14"/>
-      <c r="O51" s="15"/>
-      <c r="P51" s="15"/>
-      <c r="Q51" s="16"/>
-      <c r="R51" s="17"/>
-      <c r="S51" s="18"/>
-      <c r="T51" s="15"/>
-      <c r="U51" s="16"/>
-      <c r="V51" s="15"/>
-      <c r="W51" s="15"/>
-      <c r="X51" s="15"/>
-      <c r="Y51" s="19"/>
-      <c r="Z51" s="20"/>
-      <c r="AA51" s="4"/>
-      <c r="AB51" s="1"/>
-      <c r="AC51" s="15"/>
-      <c r="AD51" s="19">
-        <v>26</v>
-      </c>
-      <c r="AE51" s="15"/>
-      <c r="AF51" s="21">
-        <v>4.6</v>
-      </c>
-      <c r="AG51" s="22">
-        <v>0</v>
-      </c>
-      <c r="AH51" s="20"/>
-      <c r="AI51" s="16">
-        <v>0</v>
-      </c>
-      <c r="AJ51"/>
-      <c r="AK51" s="13"/>
-      <c r="AL51" s="19"/>
-      <c r="AM51" s="13"/>
-      <c r="AN51" s="13"/>
-      <c r="AO51" s="13"/>
-      <c r="AP51" s="20"/>
-      <c r="AQ51" s="19"/>
-      <c r="AR51" s="19"/>
-      <c r="AS51" s="14"/>
-      <c r="AT51" s="13"/>
-      <c r="AU51" s="13"/>
-      <c r="AV51" s="14"/>
-      <c r="AW51" s="13"/>
-      <c r="AX51" s="13"/>
-      <c r="AY51" s="13"/>
-      <c r="AZ51" s="13"/>
-      <c r="BA51" s="13"/>
-      <c r="BB51" s="13"/>
-      <c r="BC51" s="13"/>
-      <c r="BD51" s="13"/>
-      <c r="BE51" s="13"/>
-      <c r="BF51" s="13"/>
-      <c r="BG51" s="13"/>
-      <c r="BH51" s="14"/>
-      <c r="BI51" s="23"/>
-      <c r="BJ51" s="23"/>
-      <c r="BK51" s="23"/>
-      <c r="BL51" s="23"/>
-      <c r="BM51" s="23"/>
-      <c r="BN51" s="23"/>
-      <c r="BO51" s="23"/>
-      <c r="BP51" s="23"/>
-      <c r="BQ51" s="23"/>
-      <c r="BR51" s="13"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -18325,33 +18063,26 @@
     <hyperlink ref="M47" r:id="rId356" tooltip="https://www.amazon.de/b?node=13528288031"/>
     <hyperlink ref="N47" r:id="rId357"/>
     <hyperlink ref="AW47" r:id="rId358" tooltip="https://www.amazon.de/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1OG68CATOOAOD"/>
-    <hyperlink ref="C48" r:id="rId359" tooltip="https://www.amazon.de/dp/B0GH912PFJ"/>
-    <hyperlink ref="G48" r:id="rId360" tooltip="https://www.amazon.de/stores/K%C3%A4rcher/page/EFE3653A-1163-432C-A85B-0486A31C0E3D?lp_asin=B0GH912PFJ&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J48" r:id="rId361" tooltip="https://www.amazon.de/dp/B0GH912PFJ?psc=1"/>
-    <hyperlink ref="K48" r:id="rId362" tooltip="https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T3/images/I/51GeVSsTnnL._AC_US600_.jpg"/>
-    <hyperlink ref="L48" r:id="rId363" tooltip="https://www.amazon.de/dp/B0GH912PFJ"/>
+    <hyperlink ref="C48" r:id="rId359" tooltip="https://www.amazon.de/dp/B0D7HF8S2W"/>
+    <hyperlink ref="G48" r:id="rId360" tooltip="https://www.amazon.de/stores/Minthouz/page/08953CA0-3566-47FB-BCE8-A230ADB3247F?lp_asin=B0D7HF8S2W&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J48" r:id="rId361" tooltip="https://www.amazon.de/dp/B0D7HF8S2W?psc=1"/>
+    <hyperlink ref="K48" r:id="rId362" tooltip="https://images-na.ssl-images-amazon.com/images/I/61pssUlO3ZL._AC_US600_.jpg"/>
+    <hyperlink ref="L48" r:id="rId363" tooltip="https://www.amazon.de/dp/B0D7HF8S2W"/>
     <hyperlink ref="M48" r:id="rId364" tooltip="https://www.amazon.de/b?node=13528288031"/>
     <hyperlink ref="N48" r:id="rId365"/>
-    <hyperlink ref="C49" r:id="rId366" tooltip="https://www.amazon.de/dp/B0D7HF8S2W"/>
-    <hyperlink ref="G49" r:id="rId367" tooltip="https://www.amazon.de/stores/Minthouz/page/08953CA0-3566-47FB-BCE8-A230ADB3247F?lp_asin=B0D7HF8S2W&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J49" r:id="rId368" tooltip="https://www.amazon.de/dp/B0D7HF8S2W?psc=1"/>
-    <hyperlink ref="K49" r:id="rId369" tooltip="https://images-na.ssl-images-amazon.com/images/I/61pssUlO3ZL._AC_US600_.jpg"/>
-    <hyperlink ref="L49" r:id="rId370" tooltip="https://www.amazon.de/dp/B0D7HF8S2W"/>
-    <hyperlink ref="M49" r:id="rId371" tooltip="https://www.amazon.de/b?node=13528288031"/>
-    <hyperlink ref="N49" r:id="rId372"/>
-    <hyperlink ref="AW49" r:id="rId373" tooltip="https://www.amazon.de/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A33KFCZH4G272M"/>
-    <hyperlink ref="C50" r:id="rId374" tooltip="https://www.amazon.de/dp/B0F8J7PQHF"/>
-    <hyperlink ref="G50" r:id="rId375" tooltip="https://www.amazon.deundefined"/>
-    <hyperlink ref="J50" r:id="rId376" tooltip="https://www.amazon.de/dp/B0F8J7PQHF?psc=1"/>
-    <hyperlink ref="K50" r:id="rId377" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71X71xtiqiL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L50" r:id="rId378" tooltip="https://www.amazon.de/dp/B0F8J7PQHF"/>
-    <hyperlink ref="C51" r:id="rId379" tooltip="https://www.amazon.de/dp/B0F93T73PK"/>
-    <hyperlink ref="G51" r:id="rId380" tooltip="https://www.amazon.deundefined"/>
-    <hyperlink ref="J51" r:id="rId381" tooltip="https://www.amazon.de/dp/B0F93T73PK?psc=1"/>
-    <hyperlink ref="K51" r:id="rId382" tooltip="https://images-eu.ssl-images-amazon.com/images/I/719oPgCjpQL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L51" r:id="rId383" tooltip="https://www.amazon.de/dp/B0F93T73PK"/>
+    <hyperlink ref="AW48" r:id="rId366" tooltip="https://www.amazon.de/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A33KFCZH4G272M"/>
+    <hyperlink ref="C49" r:id="rId367" tooltip="https://www.amazon.de/dp/B0F8J7PQHF"/>
+    <hyperlink ref="G49" r:id="rId368" tooltip="https://www.amazon.deundefined"/>
+    <hyperlink ref="J49" r:id="rId369" tooltip="https://www.amazon.de/dp/B0F8J7PQHF?psc=1"/>
+    <hyperlink ref="K49" r:id="rId370" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71X71xtiqiL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L49" r:id="rId371" tooltip="https://www.amazon.de/dp/B0F8J7PQHF"/>
+    <hyperlink ref="C50" r:id="rId372" tooltip="https://www.amazon.de/dp/B0F93T73PK"/>
+    <hyperlink ref="G50" r:id="rId373" tooltip="https://www.amazon.deundefined"/>
+    <hyperlink ref="J50" r:id="rId374" tooltip="https://www.amazon.de/dp/B0F93T73PK?psc=1"/>
+    <hyperlink ref="K50" r:id="rId375" tooltip="https://images-eu.ssl-images-amazon.com/images/I/719oPgCjpQL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L50" r:id="rId376" tooltip="https://www.amazon.de/dp/B0F93T73PK"/>
   </hyperlinks>
-  <drawing r:id="rId384"/>
+  <drawing r:id="rId377"/>
 </worksheet>
 </file>
 
@@ -18421,7 +18152,7 @@
         <v>132.64697609001408</v>
       </c>
       <c r="G2" s="22">
-        <v>0.1401675702316412</v>
+        <v>0.14025051780254463</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18442,7 +18173,7 @@
         <v>135.15211754537597</v>
       </c>
       <c r="G3" s="22">
-        <v>0.11404632824051257</v>
+        <v>0.1141138179307624</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18463,7 +18194,7 @@
         <v>59.99013157894737</v>
       </c>
       <c r="G4" s="22">
-        <v>0.11986200098570725</v>
+        <v>0.11993293224183844</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18484,7 +18215,7 @@
         <v>63.640407784986095</v>
       </c>
       <c r="G5" s="22">
-        <v>0.10635781172991622</v>
+        <v>0.10642075155340763</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18494,18 +18225,18 @@
         </is>
       </c>
       <c r="B6" s="15">
-        <v>582</v>
+        <v>576</v>
       </c>
       <c r="C6" s="15">
-        <v>54774</v>
+        <v>54714</v>
       </c>
       <c r="D6" s="15"/>
       <c r="E6" s="15"/>
       <c r="F6" s="20">
-        <v>94.11340206185567</v>
+        <v>94.98958333333333</v>
       </c>
       <c r="G6" s="22">
-        <v>0.057368161655988174</v>
+        <v>0.05681033632508137</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18526,7 +18257,7 @@
         <v>33.879325643300795</v>
       </c>
       <c r="G7" s="22">
-        <v>0.11108920650566782</v>
+        <v>0.11115494624716442</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18547,7 +18278,7 @@
         <v>79.83870967741936</v>
       </c>
       <c r="G8" s="22">
-        <v>0.03972400197141449</v>
+        <v>0.03974750961633297</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18568,7 +18299,7 @@
         <v>83.87894736842105</v>
       </c>
       <c r="G9" s="22">
-        <v>0.037456875308033516</v>
+        <v>0.037479041325574516</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18589,7 +18320,7 @@
         <v>79.98992443324937</v>
       </c>
       <c r="G10" s="22">
-        <v>0.03913257762444554</v>
+        <v>0.03915573527961337</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18610,7 +18341,7 @@
         <v>69.0</v>
       </c>
       <c r="G11" s="22">
-        <v>0.04455396747166092</v>
+        <v>0.04458033336620969</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18631,7 +18362,7 @@
         <v>228.55696202531647</v>
       </c>
       <c r="G12" s="22">
-        <v>0.007787087235091178</v>
+        <v>0.007791695433474702</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18652,7 +18383,7 @@
         <v>51.60077519379845</v>
       </c>
       <c r="G13" s="22">
-        <v>0.02543124691966486</v>
+        <v>0.025446296478942698</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18673,7 +18404,7 @@
         <v>139.9</v>
       </c>
       <c r="G14" s="22">
-        <v>0.007885657959586003</v>
+        <v>0.007890324489594635</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18694,7 +18425,7 @@
         <v>79.47058823529412</v>
       </c>
       <c r="G15" s="22">
-        <v>0.013405618531296204</v>
+        <v>0.013413551632310878</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18715,7 +18446,7 @@
         <v>69.98684210526316</v>
       </c>
       <c r="G16" s="22">
-        <v>0.014982750123213406</v>
+        <v>0.014991616530229806</v>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18736,7 +18467,7 @@
         <v>99.99056603773585</v>
       </c>
       <c r="G17" s="22">
-        <v>0.010448496796451453</v>
+        <v>0.010454679948712891</v>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18757,7 +18488,7 @@
         <v>47.5919540229885</v>
       </c>
       <c r="G18" s="22">
-        <v>0.017151306062099556</v>
+        <v>0.01716145576486833</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18778,7 +18509,7 @@
         <v>99.0</v>
       </c>
       <c r="G19" s="22">
-        <v>0.008181370133070479</v>
+        <v>0.008186211657954433</v>
       </c>
     </row>
     <row r="20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18799,7 +18530,7 @@
         <v>59.992592592592594</v>
       </c>
       <c r="G20" s="22">
-        <v>0.01330704780680138</v>
+        <v>0.013314922576190946</v>
       </c>
     </row>
     <row r="21" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18820,7 +18551,7 @@
         <v>89.98684210526316</v>
       </c>
       <c r="G21" s="22">
-        <v>0.007491375061606703</v>
+        <v>0.007495808265114903</v>
       </c>
     </row>
     <row r="22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18841,7 +18572,7 @@
         <v>99.98245614035088</v>
       </c>
       <c r="G22" s="22">
-        <v>0.005618531296205027</v>
+        <v>0.005621856198836177</v>
       </c>
     </row>
     <row r="23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18862,7 +18593,7 @@
         <v>29.865921787709496</v>
       </c>
       <c r="G23" s="22">
-        <v>0.017644159684573682</v>
+        <v>0.017654601045467996</v>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18883,7 +18614,7 @@
         <v>69.98461538461538</v>
       </c>
       <c r="G24" s="22">
-        <v>0.006407097092163627</v>
+        <v>0.006410888647795641</v>
       </c>
     </row>
     <row r="25" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18904,7 +18635,7 @@
         <v>25.518072289156628</v>
       </c>
       <c r="G25" s="22">
-        <v>0.016362740266140957</v>
+        <v>0.016372423315908866</v>
       </c>
     </row>
     <row r="26" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18925,7 +18656,7 @@
         <v>69.91111111111111</v>
       </c>
       <c r="G26" s="22">
-        <v>0.004435682602267127</v>
+        <v>0.004438307525396982</v>
       </c>
     </row>
     <row r="27" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18946,7 +18677,7 @@
         <v>129.0</v>
       </c>
       <c r="G27" s="22">
-        <v>0.0013799901429275504</v>
+        <v>0.0013808067856790611</v>
       </c>
     </row>
     <row r="28" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18967,7 +18698,7 @@
         <v>80.0</v>
       </c>
       <c r="G28" s="22">
-        <v>0.001971414489896501</v>
+        <v>0.0019725811223986586</v>
       </c>
     </row>
     <row r="29" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -18988,7 +18719,7 @@
         <v>44.6551724137931</v>
       </c>
       <c r="G29" s="22">
-        <v>0.002858551010349926</v>
+        <v>0.002860242627478055</v>
       </c>
     </row>
     <row r="30" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19009,7 +18740,7 @@
         <v>29.945945945945947</v>
       </c>
       <c r="G30" s="22">
-        <v>0.003647116806308526</v>
+        <v>0.0036492750764375186</v>
       </c>
     </row>
     <row r="31" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19030,7 +18761,7 @@
         <v>55.0</v>
       </c>
       <c r="G31" s="22">
-        <v>0.0012814194184327255</v>
+        <v>0.0012821777295591282</v>
       </c>
     </row>
     <row r="32" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19051,7 +18782,7 @@
         <v>70.0</v>
       </c>
       <c r="G32" s="22">
-        <v>0.0009857072449482504</v>
+        <v>0.0009862905611993293</v>
       </c>
     </row>
     <row r="33" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19072,7 +18803,7 @@
         <v>80.0</v>
       </c>
       <c r="G33" s="22">
-        <v>0.00039428289797930016</v>
+        <v>0.0003945162244797317</v>
       </c>
     </row>
     <row r="34" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19093,7 +18824,7 @@
         <v>20.0</v>
       </c>
       <c r="G34" s="22">
-        <v>0.0011828486939379004</v>
+        <v>0.0011835486734391952</v>
       </c>
     </row>
     <row r="35" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19195,18 +18926,18 @@
         </is>
       </c>
       <c r="B2" s="15">
-        <v>4046</v>
+        <v>4040</v>
       </c>
       <c r="C2" s="15">
-        <v>352980</v>
+        <v>352920</v>
       </c>
       <c r="D2" s="15"/>
       <c r="E2" s="15"/>
       <c r="F2" s="20">
-        <v>87.24172021749877</v>
+        <v>87.35643564356435</v>
       </c>
       <c r="G2" s="22">
-        <v>0.3988171513060621</v>
+        <v>0.398461386724529</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19227,7 +18958,7 @@
         <v>138.29561671763506</v>
       </c>
       <c r="G3" s="22">
-        <v>0.09669788072942335</v>
+        <v>0.0967551040536542</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19248,7 +18979,7 @@
         <v>59.99013157894737</v>
       </c>
       <c r="G4" s="22">
-        <v>0.11986200098570725</v>
+        <v>0.11993293224183844</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19269,7 +19000,7 @@
         <v>63.640407784986095</v>
       </c>
       <c r="G5" s="22">
-        <v>0.10635781172991622</v>
+        <v>0.10642075155340763</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19290,7 +19021,7 @@
         <v>79.83870967741936</v>
       </c>
       <c r="G6" s="22">
-        <v>0.03972400197141449</v>
+        <v>0.03974750961633297</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19311,7 +19042,7 @@
         <v>69.0</v>
       </c>
       <c r="G7" s="22">
-        <v>0.04455396747166092</v>
+        <v>0.04458033336620969</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19332,7 +19063,7 @@
         <v>87.76842105263158</v>
       </c>
       <c r="G8" s="22">
-        <v>0.018728437654016758</v>
+        <v>0.018739520662787258</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19353,7 +19084,7 @@
         <v>51.60077519379845</v>
       </c>
       <c r="G9" s="22">
-        <v>0.02543124691966486</v>
+        <v>0.025446296478942698</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19374,7 +19105,7 @@
         <v>249.9811320754717</v>
       </c>
       <c r="G10" s="22">
-        <v>0.005224248398225727</v>
+        <v>0.0052273399743564455</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19395,7 +19126,7 @@
         <v>139.9</v>
       </c>
       <c r="G11" s="22">
-        <v>0.007885657959586003</v>
+        <v>0.007890324489594635</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19416,7 +19147,7 @@
         <v>79.47058823529412</v>
       </c>
       <c r="G12" s="22">
-        <v>0.013405618531296204</v>
+        <v>0.013413551632310878</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19437,7 +19168,7 @@
         <v>69.98684210526316</v>
       </c>
       <c r="G13" s="22">
-        <v>0.014982750123213406</v>
+        <v>0.014991616530229806</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19458,7 +19189,7 @@
         <v>99.99056603773585</v>
       </c>
       <c r="G14" s="22">
-        <v>0.010448496796451453</v>
+        <v>0.010454679948712891</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19479,7 +19210,7 @@
         <v>47.5919540229885</v>
       </c>
       <c r="G15" s="22">
-        <v>0.017151306062099556</v>
+        <v>0.01716145576486833</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19500,7 +19231,7 @@
         <v>99.0</v>
       </c>
       <c r="G16" s="22">
-        <v>0.008181370133070479</v>
+        <v>0.008186211657954433</v>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19521,7 +19252,7 @@
         <v>59.992592592592594</v>
       </c>
       <c r="G17" s="22">
-        <v>0.01330704780680138</v>
+        <v>0.013314922576190946</v>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19542,7 +19273,7 @@
         <v>89.98684210526316</v>
       </c>
       <c r="G18" s="22">
-        <v>0.007491375061606703</v>
+        <v>0.007495808265114903</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19563,7 +19294,7 @@
         <v>99.98245614035088</v>
       </c>
       <c r="G19" s="22">
-        <v>0.005618531296205027</v>
+        <v>0.005621856198836177</v>
       </c>
     </row>
     <row r="20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19584,7 +19315,7 @@
         <v>184.8846153846154</v>
       </c>
       <c r="G20" s="22">
-        <v>0.002562838836865451</v>
+        <v>0.0025643554591182564</v>
       </c>
     </row>
     <row r="21" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19605,7 +19336,7 @@
         <v>69.98461538461538</v>
       </c>
       <c r="G21" s="22">
-        <v>0.006407097092163627</v>
+        <v>0.006410888647795641</v>
       </c>
     </row>
     <row r="22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19626,7 +19357,7 @@
         <v>29.849206349206348</v>
       </c>
       <c r="G22" s="22">
-        <v>0.012419911286347955</v>
+        <v>0.01242726107111155</v>
       </c>
     </row>
     <row r="23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19647,7 +19378,7 @@
         <v>69.91111111111111</v>
       </c>
       <c r="G23" s="22">
-        <v>0.004435682602267127</v>
+        <v>0.004438307525396982</v>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19668,7 +19399,7 @@
         <v>31.983870967741936</v>
       </c>
       <c r="G24" s="22">
-        <v>0.006111384918679152</v>
+        <v>0.006115001479435842</v>
       </c>
     </row>
     <row r="25" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19689,7 +19420,7 @@
         <v>129.0</v>
       </c>
       <c r="G25" s="22">
-        <v>0.0013799901429275504</v>
+        <v>0.0013808067856790611</v>
       </c>
     </row>
     <row r="26" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19710,7 +19441,7 @@
         <v>80.0</v>
       </c>
       <c r="G26" s="22">
-        <v>0.001971414489896501</v>
+        <v>0.0019725811223986586</v>
       </c>
     </row>
     <row r="27" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19731,7 +19462,7 @@
         <v>44.6551724137931</v>
       </c>
       <c r="G27" s="22">
-        <v>0.002858551010349926</v>
+        <v>0.002860242627478055</v>
       </c>
     </row>
     <row r="28" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19752,7 +19483,7 @@
         <v>29.945945945945947</v>
       </c>
       <c r="G28" s="22">
-        <v>0.003647116806308526</v>
+        <v>0.0036492750764375186</v>
       </c>
     </row>
     <row r="29" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19773,7 +19504,7 @@
         <v>55.0</v>
       </c>
       <c r="G29" s="22">
-        <v>0.0012814194184327255</v>
+        <v>0.0012821777295591282</v>
       </c>
     </row>
     <row r="30" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19794,7 +19525,7 @@
         <v>70.0</v>
       </c>
       <c r="G30" s="22">
-        <v>0.0009857072449482504</v>
+        <v>0.0009862905611993293</v>
       </c>
     </row>
     <row r="31" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19815,7 +19546,7 @@
         <v>80.0</v>
       </c>
       <c r="G31" s="22">
-        <v>0.00039428289797930016</v>
+        <v>0.0003945162244797317</v>
       </c>
     </row>
     <row r="32" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19836,7 +19567,7 @@
         <v>20.0</v>
       </c>
       <c r="G32" s="22">
-        <v>0.0011828486939379004</v>
+        <v>0.0011835486734391952</v>
       </c>
     </row>
     <row r="33" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19857,7 +19588,7 @@
         <v>19.0</v>
       </c>
       <c r="G33" s="22">
-        <v>0.0004928536224741252</v>
+        <v>0.0004931452805996647</v>
       </c>
     </row>
     <row r="34" ht="24" customHeight="1" x14ac:dyDescent="0.25">
